--- a/excel/07简单函数与公式.xlsx
+++ b/excel/07简单函数与公式.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Desktop/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85AC2DC-6909-8845-AFD6-3074805A3CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1018305D-9BF0-F044-B3B3-72BE76A88E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="109">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -416,6 +416,22 @@
   </si>
   <si>
     <t>&lt;&gt;属于不等于 例如&lt;&gt;""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、函数参数与个数限制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公式允许的嵌套层数为64个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excel 2010中的函数参数个数限制为255个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在Excel 2003版中仅为30个参数、7层嵌套</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,7 +444,7 @@
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
     <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -562,6 +578,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -981,7 +1004,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1115,6 +1138,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -1721,16 +1747,31 @@
       <c r="G52" s="1"/>
     </row>
     <row r="53" spans="2:7">
+      <c r="B53" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="C53" s="3"/>
       <c r="E53" s="3"/>
     </row>
     <row r="54" spans="2:7">
+      <c r="B54" s="3"/>
+      <c r="C54" s="60" t="s">
+        <v>107</v>
+      </c>
       <c r="E54" s="3"/>
     </row>
     <row r="55" spans="2:7">
+      <c r="B55" s="3"/>
+      <c r="C55" s="60" t="s">
+        <v>106</v>
+      </c>
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="2:7">
+      <c r="B56" s="3"/>
+      <c r="C56" s="60" t="s">
+        <v>108</v>
+      </c>
       <c r="E56" s="3"/>
     </row>
     <row r="57" spans="2:7">
